--- a/artfynd/A 59036-2024 artfynd.xlsx
+++ b/artfynd/A 59036-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1910,6 +1910,118 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121926125</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99368</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bergsjöån, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>534769</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7235988</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>1991-08-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1991-08-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Andrahandsuppgift. Inventeringskarta från Per Löfgren sänt till Stefan Ericsson. Kan även finnas i Skogsvårdstyrelsens arkiv. "RIkligt längs Bergsjöån, båda sidorna"</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Katarina Stenman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Katarina Stenman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59036-2024 artfynd.xlsx
+++ b/artfynd/A 59036-2024 artfynd.xlsx
@@ -1915,7 +1915,7 @@
         <v>121926125</v>
       </c>
       <c r="B13" t="n">
-        <v>99368</v>
+        <v>99386</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 59036-2024 artfynd.xlsx
+++ b/artfynd/A 59036-2024 artfynd.xlsx
@@ -1915,7 +1915,7 @@
         <v>121926125</v>
       </c>
       <c r="B13" t="n">
-        <v>99386</v>
+        <v>99388</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 59036-2024 artfynd.xlsx
+++ b/artfynd/A 59036-2024 artfynd.xlsx
@@ -1915,7 +1915,7 @@
         <v>121926125</v>
       </c>
       <c r="B13" t="n">
-        <v>99388</v>
+        <v>99395</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 59036-2024 artfynd.xlsx
+++ b/artfynd/A 59036-2024 artfynd.xlsx
@@ -1915,7 +1915,7 @@
         <v>121926125</v>
       </c>
       <c r="B13" t="n">
-        <v>99395</v>
+        <v>99404</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 59036-2024 artfynd.xlsx
+++ b/artfynd/A 59036-2024 artfynd.xlsx
@@ -1915,7 +1915,7 @@
         <v>121926125</v>
       </c>
       <c r="B13" t="n">
-        <v>99430</v>
+        <v>99440</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 59036-2024 artfynd.xlsx
+++ b/artfynd/A 59036-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67153039</v>
+        <v>67199679</v>
       </c>
       <c r="B2" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534719.7971076219</v>
+        <v>534690</v>
       </c>
       <c r="R2" t="n">
-        <v>7235433.209461591</v>
+        <v>7235417</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2017-08-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-08-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67153113</v>
+        <v>67199681</v>
       </c>
       <c r="B3" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1467</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534715.1004915811</v>
+        <v>534790</v>
       </c>
       <c r="R3" t="n">
-        <v>7235439.863701339</v>
+        <v>7235460</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2017-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67153118</v>
+        <v>67199673</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534725.2691189289</v>
+        <v>534669</v>
       </c>
       <c r="R4" t="n">
-        <v>7235432.015862447</v>
+        <v>7235398</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2017-08-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-08-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67153044</v>
+        <v>67153042</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534714.1077165306</v>
+        <v>534659</v>
       </c>
       <c r="R5" t="n">
-        <v>7235417.207247854</v>
+        <v>7235362</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1034,9 @@
           <t>2017-08-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-08-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67153117</v>
+        <v>67153113</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534681.0426269309</v>
+        <v>534715</v>
       </c>
       <c r="R6" t="n">
-        <v>7235372.786159677</v>
+        <v>7235440</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1131,9 @@
           <t>2017-08-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-08-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>67153033</v>
+        <v>67199694</v>
       </c>
       <c r="B7" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534751.967300534</v>
+        <v>534733</v>
       </c>
       <c r="R7" t="n">
-        <v>7235446.588188661</v>
+        <v>7235461</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1308,21 +1228,11 @@
           <t>2017-08-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-08-09</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1331,11 +1241,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Sten</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1352,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>67199673</v>
+        <v>67153117</v>
       </c>
       <c r="B8" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534668.5728232919</v>
+        <v>534681</v>
       </c>
       <c r="R8" t="n">
-        <v>7235397.800721281</v>
+        <v>7235373</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1425,19 +1325,9 @@
           <t>2017-08-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-08-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67199717</v>
+        <v>67153118</v>
       </c>
       <c r="B9" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534725.0666537882</v>
+        <v>534725</v>
       </c>
       <c r="R9" t="n">
-        <v>7235449.206656525</v>
+        <v>7235432</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1537,19 +1422,9 @@
           <t>2017-08-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2017-08-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,12 +1454,7 @@
         <v>67199697</v>
       </c>
       <c r="B10" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534690.9997169554</v>
+        <v>534691</v>
       </c>
       <c r="R10" t="n">
-        <v>7235418.612668228</v>
+        <v>7235419</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1649,19 +1519,9 @@
           <t>2017-08-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2017-08-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,53 +1548,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>67199679</v>
+        <v>121926125</v>
       </c>
       <c r="B11" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>2082</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stennäs, Bergsjöån, Ås lm</t>
+          <t>Bergsjöån, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534689.7600901581</v>
+        <v>534769</v>
       </c>
       <c r="R11" t="n">
-        <v>7235416.920687521</v>
+        <v>7235988</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,22 +1617,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2017-08-09</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1991-08-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2017-08-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1991-08-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Andrahandsuppgift. Inventeringskarta från Per Löfgren sänt till Stefan Ericsson. Kan även finnas i Skogsvårdstyrelsens arkiv. "RIkligt längs Bergsjöån, båda sidorna"</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,55 +1636,51 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Katarina Stenman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Via Katarina Stenman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>67199694</v>
+        <v>67153044</v>
       </c>
       <c r="B12" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534732.9091526421</v>
+        <v>534714</v>
       </c>
       <c r="R12" t="n">
-        <v>7235460.621315259</v>
+        <v>7235417</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1873,19 +1723,9 @@
           <t>2017-08-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2017-08-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,15 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121926125</v>
+        <v>67153039</v>
       </c>
       <c r="B13" t="n">
-        <v>99440</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,41 +1763,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2082</v>
+        <v>6439</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergsjöån, Ås lm</t>
+          <t>Stennäs, Bergsjöån, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534769</v>
+        <v>534720</v>
       </c>
       <c r="R13" t="n">
-        <v>7235988</v>
+        <v>7235433</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1986,17 +1817,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1991-08-01</t>
+          <t>2017-08-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1991-08-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Andrahandsuppgift. Inventeringskarta från Per Löfgren sänt till Stefan Ericsson. Kan även finnas i Skogsvårdstyrelsens arkiv. "RIkligt längs Bergsjöån, båda sidorna"</t>
+          <t>2017-08-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2005,22 +1831,414 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Katarina Stenman</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Katarina Stenman</t>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>67199717</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stennäs, Bergsjöån, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>534725</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7235449</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2017-08-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2017-08-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>67153033</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stennäs, Bergsjöån, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>534752</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7235447</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2017-08-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2017-08-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Sten</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>67153034</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stennäs, Bergsjöån, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>534779</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7235472</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2017-08-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2017-08-09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>67153093</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stennäs, Bergsjöån, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>534685</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7235372</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2017-08-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2017-08-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
